--- a/backtest/results_us100/七星美股版_实盘交易记录.xlsx
+++ b/backtest/results_us100/七星美股版_实盘交易记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="47">
   <si>
     <t>交易日期</t>
   </si>
@@ -46,6 +46,36 @@
     <t>2026-08-06</t>
   </si>
   <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
     <t>EOG</t>
   </si>
   <si>
@@ -55,6 +85,39 @@
     <t>AMT</t>
   </si>
   <si>
+    <t>ZS</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>IONQ</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>RKLB</t>
+  </si>
+  <si>
+    <t>SPCX</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
     <t>买入</t>
   </si>
   <si>
@@ -71,6 +134,27 @@
   </si>
   <si>
     <t>不在今日目标</t>
+  </si>
+  <si>
+    <t>持久化: 排名1</t>
+  </si>
+  <si>
+    <t>持久化: 排名3</t>
+  </si>
+  <si>
+    <t>持久化: 排名4</t>
+  </si>
+  <si>
+    <t>持久化: 排名5</t>
+  </si>
+  <si>
+    <t>持久化: 排名7</t>
+  </si>
+  <si>
+    <t>持久化: 排名6</t>
+  </si>
+  <si>
+    <t>NDX5恐慌空仓</t>
   </si>
 </sst>
 </file>
@@ -428,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -462,13 +546,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>143.76</v>
@@ -480,7 +564,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -488,13 +572,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>296.92</v>
@@ -506,7 +590,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -514,13 +598,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>174.77</v>
@@ -532,7 +616,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -540,13 +624,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>170.94</v>
@@ -558,7 +642,683 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6">
+        <v>140.52</v>
+      </c>
+      <c r="F6">
+        <v>48</v>
+      </c>
+      <c r="G6">
+        <v>1.850703026003797</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>175.36</v>
+      </c>
+      <c r="F7">
+        <v>39</v>
+      </c>
+      <c r="G7">
+        <v>1.290286230231872</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <v>126.13</v>
+      </c>
+      <c r="F8">
+        <v>55</v>
+      </c>
+      <c r="G8">
+        <v>0.8744027938204831</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9">
+        <v>115.71</v>
+      </c>
+      <c r="F9">
+        <v>60</v>
+      </c>
+      <c r="G9">
+        <v>0.5494489168637116</v>
+      </c>
+      <c r="H9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10">
+        <v>392.73</v>
+      </c>
+      <c r="F10">
+        <v>17</v>
+      </c>
+      <c r="G10">
+        <v>0.5675635282792316</v>
+      </c>
+      <c r="H10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11">
+        <v>46.48</v>
+      </c>
+      <c r="F11">
+        <v>150</v>
+      </c>
+      <c r="G11">
+        <v>8.156762029709951</v>
+      </c>
+      <c r="H11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12">
+        <v>146.89</v>
+      </c>
+      <c r="F12">
+        <v>47</v>
+      </c>
+      <c r="G12">
+        <v>6.871727331450243</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13">
+        <v>357.14</v>
+      </c>
+      <c r="F13">
+        <v>17</v>
+      </c>
+      <c r="G13">
+        <v>0.5675635282792316</v>
+      </c>
+      <c r="H13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>838.28</v>
+      </c>
+      <c r="F14">
+        <v>8</v>
+      </c>
+      <c r="G14">
+        <v>4.291107478203252</v>
+      </c>
+      <c r="H14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15">
+        <v>286</v>
+      </c>
+      <c r="F15">
+        <v>23</v>
+      </c>
+      <c r="G15">
+        <v>1.048568944225358</v>
+      </c>
+      <c r="H15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="F16">
+        <v>95</v>
+      </c>
+      <c r="G16">
+        <v>4.490398840085638</v>
+      </c>
+      <c r="H16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17">
+        <v>69.37</v>
+      </c>
+      <c r="F17">
+        <v>95</v>
+      </c>
+      <c r="G17">
+        <v>4.490398840085638</v>
+      </c>
+      <c r="H17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>135.76</v>
+      </c>
+      <c r="F18">
+        <v>51</v>
+      </c>
+      <c r="G18">
+        <v>7.677801960298933</v>
+      </c>
+      <c r="H18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19">
+        <v>908.0599999999999</v>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>4.291107478203252</v>
+      </c>
+      <c r="H19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>81.91</v>
+      </c>
+      <c r="F20">
+        <v>85</v>
+      </c>
+      <c r="G20">
+        <v>3.650597275283464</v>
+      </c>
+      <c r="H20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21">
+        <v>152.61</v>
+      </c>
+      <c r="F21">
+        <v>47</v>
+      </c>
+      <c r="G21">
+        <v>6.871727331450243</v>
+      </c>
+      <c r="H21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22">
+        <v>917.05</v>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22">
+        <v>4.101054724283061</v>
+      </c>
+      <c r="H22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
         <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23">
+        <v>39.66</v>
+      </c>
+      <c r="F23">
+        <v>150</v>
+      </c>
+      <c r="G23">
+        <v>8.156762029709951</v>
+      </c>
+      <c r="H23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24">
+        <v>102.89</v>
+      </c>
+      <c r="F24">
+        <v>68</v>
+      </c>
+      <c r="G24">
+        <v>4.548675345807821</v>
+      </c>
+      <c r="H24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25">
+        <v>176.29</v>
+      </c>
+      <c r="F25">
+        <v>39</v>
+      </c>
+      <c r="G25">
+        <v>1.290286230231872</v>
+      </c>
+      <c r="H25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26">
+        <v>139.32</v>
+      </c>
+      <c r="F26">
+        <v>55</v>
+      </c>
+      <c r="G26">
+        <v>0.8744027938204831</v>
+      </c>
+      <c r="H26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27">
+        <v>125.76</v>
+      </c>
+      <c r="F27">
+        <v>60</v>
+      </c>
+      <c r="G27">
+        <v>0.5494489168637116</v>
+      </c>
+      <c r="H27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28">
+        <v>140.45</v>
+      </c>
+      <c r="F28">
+        <v>51</v>
+      </c>
+      <c r="G28">
+        <v>7.677801960298933</v>
+      </c>
+      <c r="H28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29">
+        <v>82.61</v>
+      </c>
+      <c r="F29">
+        <v>85</v>
+      </c>
+      <c r="G29">
+        <v>3.650597275283464</v>
+      </c>
+      <c r="H29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30">
+        <v>860</v>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>4.101054724283061</v>
+      </c>
+      <c r="H30" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31">
+        <v>106.97</v>
+      </c>
+      <c r="F31">
+        <v>68</v>
+      </c>
+      <c r="G31">
+        <v>4.548675345807821</v>
+      </c>
+      <c r="H31" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/backtest/results_us100/七星美股版_实盘交易记录.xlsx
+++ b/backtest/results_us100/七星美股版_实盘交易记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="50">
   <si>
     <t>交易日期</t>
   </si>
@@ -76,6 +76,9 @@
     <t>2026-09-02</t>
   </si>
   <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
     <t>EOG</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>HOOD</t>
   </si>
   <si>
+    <t>MU</t>
+  </si>
+  <si>
     <t>买入</t>
   </si>
   <si>
@@ -155,6 +161,9 @@
   </si>
   <si>
     <t>NDX5恐慌空仓</t>
+  </si>
+  <si>
+    <t>持久化: 排名2</t>
   </si>
 </sst>
 </file>
@@ -512,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -546,13 +555,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>143.76</v>
@@ -564,7 +573,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -572,13 +581,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>296.92</v>
@@ -590,7 +599,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -598,13 +607,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4">
         <v>174.77</v>
@@ -616,7 +625,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -624,13 +633,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>170.94</v>
@@ -642,7 +651,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -650,13 +659,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>140.52</v>
@@ -668,7 +677,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -676,13 +685,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>175.36</v>
@@ -694,7 +703,7 @@
         <v>1.290286230231872</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -702,13 +711,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>126.13</v>
@@ -720,7 +729,7 @@
         <v>0.8744027938204831</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -728,13 +737,13 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <v>115.71</v>
@@ -746,7 +755,7 @@
         <v>0.5494489168637116</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -754,13 +763,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>392.73</v>
@@ -772,7 +781,7 @@
         <v>0.5675635282792316</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -780,13 +789,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>46.48</v>
@@ -798,7 +807,7 @@
         <v>8.156762029709951</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -806,13 +815,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>146.89</v>
@@ -824,7 +833,7 @@
         <v>6.871727331450243</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -832,13 +841,13 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>357.14</v>
@@ -850,7 +859,7 @@
         <v>0.5675635282792316</v>
       </c>
       <c r="H13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -858,13 +867,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>838.28</v>
@@ -876,7 +885,7 @@
         <v>4.291107478203252</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -884,13 +893,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E15">
         <v>286</v>
@@ -902,7 +911,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -910,13 +919,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>73.09999999999999</v>
@@ -928,7 +937,7 @@
         <v>4.490398840085638</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -936,13 +945,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E17">
         <v>69.37</v>
@@ -954,7 +963,7 @@
         <v>4.490398840085638</v>
       </c>
       <c r="H17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -962,13 +971,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E18">
         <v>135.76</v>
@@ -980,7 +989,7 @@
         <v>7.677801960298933</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -988,13 +997,13 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>908.0599999999999</v>
@@ -1006,7 +1015,7 @@
         <v>4.291107478203252</v>
       </c>
       <c r="H19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1014,13 +1023,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>81.91</v>
@@ -1032,7 +1041,7 @@
         <v>3.650597275283464</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1040,13 +1049,13 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E21">
         <v>152.61</v>
@@ -1058,7 +1067,7 @@
         <v>6.871727331450243</v>
       </c>
       <c r="H21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1066,13 +1075,13 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22">
         <v>917.05</v>
@@ -1084,7 +1093,7 @@
         <v>4.101054724283061</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1092,13 +1101,13 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>39.66</v>
@@ -1110,7 +1119,7 @@
         <v>8.156762029709951</v>
       </c>
       <c r="H23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1118,13 +1127,13 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E24">
         <v>102.89</v>
@@ -1136,7 +1145,7 @@
         <v>4.548675345807821</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1144,13 +1153,13 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E25">
         <v>176.29</v>
@@ -1162,7 +1171,7 @@
         <v>1.290286230231872</v>
       </c>
       <c r="H25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1170,13 +1179,13 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E26">
         <v>139.32</v>
@@ -1188,7 +1197,7 @@
         <v>0.8744027938204831</v>
       </c>
       <c r="H26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1196,13 +1205,13 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E27">
         <v>125.76</v>
@@ -1214,7 +1223,7 @@
         <v>0.5494489168637116</v>
       </c>
       <c r="H27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1222,13 +1231,13 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E28">
         <v>140.45</v>
@@ -1240,7 +1249,7 @@
         <v>7.677801960298933</v>
       </c>
       <c r="H28" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1248,13 +1257,13 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E29">
         <v>82.61</v>
@@ -1266,7 +1275,7 @@
         <v>3.650597275283464</v>
       </c>
       <c r="H29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1274,13 +1283,13 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <v>860</v>
@@ -1292,7 +1301,7 @@
         <v>4.101054724283061</v>
       </c>
       <c r="H30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1300,13 +1309,13 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E31">
         <v>106.97</v>
@@ -1318,6 +1327,188 @@
         <v>4.548675345807821</v>
       </c>
       <c r="H31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32">
+        <v>129.35</v>
+      </c>
+      <c r="F32">
+        <v>54</v>
+      </c>
+      <c r="G32">
+        <v>13.60666220243627</v>
+      </c>
+      <c r="H32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33">
+        <v>144.25</v>
+      </c>
+      <c r="F33">
+        <v>48</v>
+      </c>
+      <c r="G33">
+        <v>6.582518255184114</v>
+      </c>
+      <c r="H33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34">
+        <v>123.23</v>
+      </c>
+      <c r="F34">
+        <v>56</v>
+      </c>
+      <c r="G34">
+        <v>5.712362312360674</v>
+      </c>
+      <c r="H34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35">
+        <v>148.95</v>
+      </c>
+      <c r="F35">
+        <v>46</v>
+      </c>
+      <c r="G35">
+        <v>3.492246342195308</v>
+      </c>
+      <c r="H35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36">
+        <v>82.47</v>
+      </c>
+      <c r="F36">
+        <v>84</v>
+      </c>
+      <c r="G36">
+        <v>2.542131667306065</v>
+      </c>
+      <c r="H36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37">
+        <v>849.61</v>
+      </c>
+      <c r="F37">
+        <v>8</v>
+      </c>
+      <c r="G37">
+        <v>1.638536449057692</v>
+      </c>
+      <c r="H37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38">
+        <v>946.45</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>1.104587343460544</v>
+      </c>
+      <c r="H38" t="s">
         <v>46</v>
       </c>
     </row>

--- a/backtest/results_us100/七星美股版_实盘交易记录.xlsx
+++ b/backtest/results_us100/七星美股版_实盘交易记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="51">
   <si>
     <t>交易日期</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
   </si>
   <si>
     <t>EOG</t>
@@ -521,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -555,13 +558,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>143.76</v>
@@ -573,7 +576,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -581,13 +584,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>296.92</v>
@@ -599,7 +602,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -607,13 +610,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>174.77</v>
@@ -625,7 +628,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -633,13 +636,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>170.94</v>
@@ -651,7 +654,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -659,13 +662,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>140.52</v>
@@ -677,7 +680,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -685,13 +688,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>175.36</v>
@@ -703,7 +706,7 @@
         <v>1.290286230231872</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -711,13 +714,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>126.13</v>
@@ -729,7 +732,7 @@
         <v>0.8744027938204831</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -737,13 +740,13 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>115.71</v>
@@ -755,7 +758,7 @@
         <v>0.5494489168637116</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -763,13 +766,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <v>392.73</v>
@@ -781,7 +784,7 @@
         <v>0.5675635282792316</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -789,13 +792,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>46.48</v>
@@ -807,7 +810,7 @@
         <v>8.156762029709951</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -815,13 +818,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>146.89</v>
@@ -833,7 +836,7 @@
         <v>6.871727331450243</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -841,13 +844,13 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>357.14</v>
@@ -859,7 +862,7 @@
         <v>0.5675635282792316</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -867,13 +870,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>838.28</v>
@@ -885,7 +888,7 @@
         <v>4.291107478203252</v>
       </c>
       <c r="H14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -893,13 +896,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15">
         <v>286</v>
@@ -911,7 +914,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -919,13 +922,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>73.09999999999999</v>
@@ -937,7 +940,7 @@
         <v>4.490398840085638</v>
       </c>
       <c r="H16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -945,13 +948,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17">
         <v>69.37</v>
@@ -963,7 +966,7 @@
         <v>4.490398840085638</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -971,13 +974,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18">
         <v>135.76</v>
@@ -989,7 +992,7 @@
         <v>7.677801960298933</v>
       </c>
       <c r="H18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -997,13 +1000,13 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>908.0599999999999</v>
@@ -1015,7 +1018,7 @@
         <v>4.291107478203252</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1023,13 +1026,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>81.91</v>
@@ -1041,7 +1044,7 @@
         <v>3.650597275283464</v>
       </c>
       <c r="H20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1049,13 +1052,13 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>152.61</v>
@@ -1067,7 +1070,7 @@
         <v>6.871727331450243</v>
       </c>
       <c r="H21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1075,13 +1078,13 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22">
         <v>917.05</v>
@@ -1093,7 +1096,7 @@
         <v>4.101054724283061</v>
       </c>
       <c r="H22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1101,13 +1104,13 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E23">
         <v>39.66</v>
@@ -1119,7 +1122,7 @@
         <v>8.156762029709951</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1127,13 +1130,13 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24">
         <v>102.89</v>
@@ -1145,7 +1148,7 @@
         <v>4.548675345807821</v>
       </c>
       <c r="H24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1153,13 +1156,13 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25">
         <v>176.29</v>
@@ -1171,7 +1174,7 @@
         <v>1.290286230231872</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1179,13 +1182,13 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E26">
         <v>139.32</v>
@@ -1197,7 +1200,7 @@
         <v>0.8744027938204831</v>
       </c>
       <c r="H26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1205,13 +1208,13 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E27">
         <v>125.76</v>
@@ -1223,7 +1226,7 @@
         <v>0.5494489168637116</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1231,13 +1234,13 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E28">
         <v>140.45</v>
@@ -1249,7 +1252,7 @@
         <v>7.677801960298933</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1257,13 +1260,13 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E29">
         <v>82.61</v>
@@ -1275,7 +1278,7 @@
         <v>3.650597275283464</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1283,13 +1286,13 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30">
         <v>860</v>
@@ -1301,7 +1304,7 @@
         <v>4.101054724283061</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1309,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>106.97</v>
@@ -1327,7 +1330,7 @@
         <v>4.548675345807821</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1335,13 +1338,13 @@
         <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E32">
         <v>129.35</v>
@@ -1353,7 +1356,7 @@
         <v>13.60666220243627</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1361,13 +1364,13 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E33">
         <v>144.25</v>
@@ -1379,7 +1382,7 @@
         <v>6.582518255184114</v>
       </c>
       <c r="H33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1387,13 +1390,13 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E34">
         <v>123.23</v>
@@ -1405,7 +1408,7 @@
         <v>5.712362312360674</v>
       </c>
       <c r="H34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1413,13 +1416,13 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E35">
         <v>148.95</v>
@@ -1431,7 +1434,7 @@
         <v>3.492246342195308</v>
       </c>
       <c r="H35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1439,13 +1442,13 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E36">
         <v>82.47</v>
@@ -1457,7 +1460,7 @@
         <v>2.542131667306065</v>
       </c>
       <c r="H36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1465,13 +1468,13 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E37">
         <v>849.61</v>
@@ -1483,7 +1486,7 @@
         <v>1.638536449057692</v>
       </c>
       <c r="H37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1491,13 +1494,13 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E38">
         <v>946.45</v>
@@ -1509,7 +1512,59 @@
         <v>1.104587343460544</v>
       </c>
       <c r="H38" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39">
+        <v>872.74</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>1.638536449057692</v>
+      </c>
+      <c r="H39" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40">
+        <v>168.7</v>
+      </c>
+      <c r="F40">
+        <v>41</v>
+      </c>
+      <c r="G40">
+        <v>0.5870721095223653</v>
+      </c>
+      <c r="H40" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
